--- a/Revision/01_需蔡老師補做資料表/table4_external_validation_paper_friendly.xlsx
+++ b/Revision/01_需蔡老師補做資料表/table4_external_validation_paper_friendly.xlsx
@@ -493,52 +493,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.887 (0.879-0.895)</t>
+          <t>0.898 (0.889-0.906)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.828 (0.821-0.836)</t>
+          <t>0.848 (0.841-0.856)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.856 (0.836-0.878)</t>
+          <t>0.855 (0.836-0.875)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.482 (0.461-0.505)</t>
+          <t>0.567 (0.545-0.590)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.482 (0.461-0.505)</t>
+          <t>0.567 (0.545-0.590)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.968 (0.963-0.973)</t>
+          <t>0.961 (0.956-0.967)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.856 (0.836-0.878)</t>
+          <t>0.855 (0.836-0.875)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.823 (0.817-0.829)</t>
+          <t>0.847 (0.840-0.854)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.617 (0.596-0.637)</t>
+          <t>0.682 (0.663-0.701)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.122 (0.118-0.125)</t>
+          <t>0.112 (0.108-0.116)</t>
         </is>
       </c>
     </row>
@@ -550,52 +550,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.805 (0.794-0.816)</t>
+          <t>0.869 (0.859-0.878)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.744 (0.737-0.751)</t>
+          <t>0.822 (0.813-0.830)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.648 (0.616-0.682)</t>
+          <t>0.772 (0.750-0.794)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.235 (0.215-0.254)</t>
+          <t>0.536 (0.513-0.558)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.235 (0.215-0.254)</t>
+          <t>0.536 (0.513-0.558)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.949 (0.943-0.955)</t>
+          <t>0.937 (0.929-0.944)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.648 (0.616-0.682)</t>
+          <t>0.772 (0.750-0.794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.755 (0.750-0.760)</t>
+          <t>0.834 (0.827-0.841)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.345 (0.319-0.367)</t>
+          <t>0.633 (0.613-0.652)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.162 (0.159-0.166)</t>
+          <t>0.129 (0.124-0.133)</t>
         </is>
       </c>
     </row>
@@ -607,52 +607,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.886 (0.878-0.895)</t>
+          <t>0.894 (0.885-0.902)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.831 (0.824-0.838)</t>
+          <t>0.843 (0.835-0.851)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.853 (0.834-0.874)</t>
+          <t>0.857 (0.837-0.876)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.495 (0.473-0.517)</t>
+          <t>0.544 (0.520-0.565)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.495 (0.473-0.517)</t>
+          <t>0.544 (0.520-0.565)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.966 (0.961-0.971)</t>
+          <t>0.963 (0.958-0.969)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.853 (0.834-0.874)</t>
+          <t>0.857 (0.837-0.876)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.827 (0.820-0.833)</t>
+          <t>0.840 (0.833-0.847)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.627 (0.606-0.646)</t>
+          <t>0.665 (0.645-0.684)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.125 (0.121-0.128)</t>
+          <t>0.117 (0.114-0.121)</t>
         </is>
       </c>
     </row>
@@ -664,52 +664,52 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.862 (0.852-0.872)</t>
+          <t>0.878 (0.868-0.887)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.817 (0.809-0.825)</t>
+          <t>0.838 (0.830-0.846)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.773 (0.752-0.797)</t>
+          <t>0.813 (0.793-0.834)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.513 (0.490-0.534)</t>
+          <t>0.563 (0.541-0.586)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.513 (0.490-0.534)</t>
+          <t>0.563 (0.541-0.586)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.940 (0.932-0.947)</t>
+          <t>0.948 (0.941-0.955)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.773 (0.752-0.797)</t>
+          <t>0.813 (0.793-0.834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.828 (0.821-0.834)</t>
+          <t>0.844 (0.837-0.851)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.616 (0.596-0.636)</t>
+          <t>0.666 (0.646-0.684)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.128 (0.124-0.133)</t>
+          <t>0.119 (0.114-0.124)</t>
         </is>
       </c>
     </row>
@@ -721,52 +721,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.807 (0.796-0.818)</t>
+          <t>0.869 (0.859-0.878)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.745 (0.738-0.752)</t>
+          <t>0.822 (0.813-0.830)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.655 (0.621-0.690)</t>
+          <t>0.772 (0.750-0.794)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.229 (0.211-0.248)</t>
+          <t>0.536 (0.513-0.558)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.229 (0.211-0.248)</t>
+          <t>0.536 (0.513-0.558)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.952 (0.946-0.957)</t>
+          <t>0.937 (0.929-0.944)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.655 (0.621-0.690)</t>
+          <t>0.772 (0.750-0.794)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.755 (0.750-0.759)</t>
+          <t>0.834 (0.827-0.841)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.339 (0.316-0.362)</t>
+          <t>0.633 (0.613-0.652)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.163 (0.159-0.166)</t>
+          <t>0.129 (0.124-0.133)</t>
         </is>
       </c>
     </row>
@@ -778,52 +778,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.806 (0.795-0.817)</t>
+          <t>0.867 (0.857-0.877)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.745 (0.738-0.752)</t>
+          <t>0.821 (0.813-0.829)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.657 (0.623-0.692)</t>
+          <t>0.776 (0.754-0.799)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.228 (0.209-0.247)</t>
+          <t>0.528 (0.505-0.550)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.228 (0.209-0.247)</t>
+          <t>0.528 (0.505-0.550)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.952 (0.946-0.958)</t>
+          <t>0.939 (0.931-0.946)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.657 (0.623-0.692)</t>
+          <t>0.776 (0.754-0.799)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.754 (0.750-0.759)</t>
+          <t>0.832 (0.825-0.839)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.338 (0.314-0.363)</t>
+          <t>0.628 (0.608-0.648)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.163 (0.159-0.166)</t>
+          <t>0.130 (0.125-0.134)</t>
         </is>
       </c>
     </row>
@@ -835,52 +835,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.805 (0.795-0.817)</t>
+          <t>0.868 (0.858-0.878)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.745 (0.738-0.751)</t>
+          <t>0.821 (0.813-0.829)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.656 (0.623-0.691)</t>
+          <t>0.774 (0.752-0.796)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.227 (0.208-0.245)</t>
+          <t>0.531 (0.508-0.553)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.227 (0.208-0.245)</t>
+          <t>0.531 (0.508-0.553)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.952 (0.946-0.958)</t>
+          <t>0.938 (0.930-0.945)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.656 (0.623-0.691)</t>
+          <t>0.774 (0.752-0.796)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.754 (0.750-0.759)</t>
+          <t>0.833 (0.826-0.839)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.338 (0.314-0.361)</t>
+          <t>0.630 (0.609-0.649)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.163 (0.160-0.166)</t>
+          <t>0.129 (0.125-0.134)</t>
         </is>
       </c>
     </row>
@@ -892,52 +892,52 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.806 (0.795-0.817)</t>
+          <t>0.868 (0.858-0.877)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.745 (0.738-0.752)</t>
+          <t>0.821 (0.813-0.829)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.658 (0.623-0.692)</t>
+          <t>0.775 (0.753-0.797)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.229 (0.209-0.247)</t>
+          <t>0.529 (0.506-0.552)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.229 (0.209-0.247)</t>
+          <t>0.529 (0.506-0.552)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.952 (0.946-0.958)</t>
+          <t>0.938 (0.931-0.946)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.658 (0.623-0.692)</t>
+          <t>0.775 (0.753-0.797)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.755 (0.750-0.759)</t>
+          <t>0.832 (0.826-0.839)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.339 (0.315-0.363)</t>
+          <t>0.629 (0.609-0.649)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.163 (0.160-0.166)</t>
+          <t>0.129 (0.125-0.134)</t>
         </is>
       </c>
     </row>
